--- a/StudentData/Assessments/Unit6/TechGearTouchstone/techgear_sales_data.xlsx
+++ b/StudentData/Assessments/Unit6/TechGearTouchstone/techgear_sales_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28605"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30105"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Touchstones\Touchstone2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{FAB9909E-7CEE-4845-9B94-504C4B621D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7465EB0E-7237-410B-84BB-76E9C2B61A68}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF739014-CBF7-4F0D-9F8F-2B1ECFCF3335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1747,15 +1747,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb71b97d-9a65-4f5a-80e4-73af0d9029ad">
@@ -1769,14 +1760,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A41A431-056C-4B3A-92C5-840CF5AA6DB3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9039B1F-6916-4B06-90F6-BBE24E152453}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0ADB9BF-1AA4-40FC-B81F-93ED89B37B41}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0ADB9BF-1AA4-40FC-B81F-93ED89B37B41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9039B1F-6916-4B06-90F6-BBE24E152453}"/>
 </file>